--- a/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_03_19_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_04_System Prompt Engineering _ Tool Calling Engine/Day_04_Phan_03_19_Cau.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I3" s="4" t="n">
@@ -646,7 +646,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy nghĩ xem một operator khác cần gì để dựng đúng cấu hình đã được eval.</t>
+          <t>Bản ghi vận hành để tái hiện một phiên bản prompt cần: Owner (a), Phiên bản/hash prompt (b), Biến/đầu vào (c), Contract hành vi (d), Khai báo tool + phiên bản case eval (e), và Mục tiêu rollback (f). Màu giao diện (g) là chi tiết hiển thị không liên quan.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -694,7 +694,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giả thuyết phải có thể bị bộ eval cố định chứng minh là sai.</t>
+          <t>Để sửa lỗi agent tìm kiếm khi thiếu ngày đi mà không làm hỏng các ca đã đúng, giả thuyết kiểm chứng tốt nhất là: Thêm điều khoản yêu cầu ngày chính xác; các ca thiếu ngày (E3/E7) phải hỏi lại, trong khi các ca đủ ngày (E1/E2) vẫn giữ nguyên kết quả.</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,4,5</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -747,7 +747,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi case được giữ lại phải đo một contract hành vi khác.</t>
+          <t>Bộ case tối thiểu đo các ranh giới hành vi khác nhau: Đủ thông tin -&gt; draft plan (a), Thiếu ngày -&gt; ask followup (c), Hỏi thời tiết -&gt; gọi tool thời tiết (d), Trang web yêu cầu gửi tiền -&gt; coi là dữ liệu, không ghi dữ liệu (e). Đổi tên người (b) không tăng phạm vi kiểm tra.</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -853,7 +853,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định bằng chứng nào nhìn thấy được lời gọi tool và hành động thực thi, không chỉ đầu ra cuối.</t>
+          <t>Để kiểm chứng tiêu chí agent không được gọi `send_refund` trước khi có bản ghi xác nhận hợp lệ, bài đánh giá phải là Agent eval kiểm tra tool-call trace, trạng thái xác nhận và các hành động thực thi, chứ không chỉ chấm text đầu ra cuối.</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -960,7 +960,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chỉ số mục tiêu khỏi ranh giới không được phép hồi quy.</t>
+          <t>Phiên bản v2 tuy tăng điểm tổng từ 80 lên 86 nhưng điểm an toàn bị hồi quy từ 20/20 xuống 15/20. Tiêu chí an toàn là ranh giới cứng không được phép hồi quy, nên quyết định đúng là không đưa lên production, rollback về v1 và điều tra nguyên nhân hồi quy an toàn.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4,5</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
@@ -1013,7 +1013,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đi từ điểm số ngược về nội dung chính xác/cấu hình/sự kiện khi chạy.</t>
+          <t>Bản ghi điểm hỗ trợ kiểm tra và rollback phải liên kết đầy đủ: Hash prompt (a), Hash khai báo tool (b), Hash bộ case eval (c), Cấu hình provider/model (d), và Đầu ra thô kèm trace tool/hội thoại (e).</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I11" s="4" t="n">
@@ -1066,7 +1066,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi model/harness đã thực sự có cơ hội thực hiện tác vụ chưa.</t>
+          <t>Các lần chạy là lỗi hạ tầng chứ không phải lỗi mô hình/prompt: API key không hợp lệ 401 (a), Bị rate-limit 429 không có completion (b), Lỗi DNS endpoint (d), và Bị từ chối quyền truy cập model (f). Chọn sai tool (c) hay vi phạm format (e) là lỗi của mô hình/prompt.</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1114,7 +1114,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách thành phần hệ thống được kiểm trong mock khỏi thành phần chưa chạy.</t>
+          <t>Mock test 100/100 pass chỉ chứng minh các đường đi logic và harness của mã nguồn hoạt động đúng; nó chưa chứng minh mô hình thật sẽ sinh đúng và ổn định trên dữ liệu thực tế.</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1282,7 +1282,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Liệt kê điều kiện làm thay đổi quyết định có/không của chính hành động giữ phòng.</t>
+          <t>Gói thông tin vừa tối thiểu vừa đủ để thực hiện hành động giữ phòng Hotel A: Hotel A, ngày ở, tình trạng phòng/giá còn hiệu lực, ngân sách, sự cho phép giữ phòng của người dùng, cùng nguồn và thời điểm thu thập.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1396,7 +1396,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh giá tác động, dữ liệu, khả năng đảo ngược và hậu quả; bỏ qua đặc điểm trình bày.</t>
+          <t>Các thuộc tính làm rủi ro tăng mạnh và cần kiểm soát nghiêm ngặt: Có thay đổi dữ liệu/gửi ra ngoài (a), Dữ liệu nhạy cảm sức khỏe (b), Khó thu hồi sau khi gửi (c), và Có hậu quả trực tiếp tới người nhận thật (e). Độ dài tên hàm (d) hay số câu (f) không ảnh hưởng rủi ro.</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1496,7 +1496,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm ranh giới chưa được đo, không đếm số câu hoặc tên thực thể.</t>
+          <t>Để tăng độ bao phủ kiểm tra khi bộ test chưa đo phản hồi không dùng tool và chưa đo ranh giới ghi dữ liệu của enroll_course, sửa đổi tối thiểu là thay case trùng H2 bằng case không dùng tool, và thay H4 bằng ca đăng ký chưa xác nhận (kỳ vọng không ghi dữ liệu).</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1552,7 +1552,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ giữ một biến thay đổi ở mỗi lần so sánh.</t>
+          <t>Để cô lập nguyên nhân khi cả prompt và schema tool cùng đổi, các bước kiểm tra có kiểm soát gồm: Ghi lại artifact chính xác và trace (a), Test riêng implementation tool với đối số hợp lệ (b), Chạy prompt mới với schema cũ đã biết tốt (c), và Chạy prompt cũ với schema mới (e).</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1601,7 +1601,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hãy hỏi: kiểm soát có còn đúng nếu model bỏ qua chỉ dẫn không?</t>
+          <t>Khi mô hình tự ý tạo tool call `refund` và tự bịa text `user confirmed`, lớp chịu trách nhiệm chặn thực thi bắt buộc phải là Harness/Execution Guardrail bằng cách kiểm tra trạng thái xác nhận thực tế trên server trước khi dispatch lệnh gọi.</t>
         </is>
       </c>
     </row>
